--- a/HVDC Converter Station/Connections.xlsx
+++ b/HVDC Converter Station/Connections.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -13,9 +13,722 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="236">
+  <si>
+    <t>35kV Reactor Interface</t>
+  </si>
+  <si>
+    <t>No. 2</t>
+  </si>
+  <si>
+    <t>No. 1</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>S2+LRI1A</t>
+  </si>
+  <si>
+    <t>S2+LRI1B</t>
+  </si>
+  <si>
+    <t>S2+LRI2A</t>
+  </si>
+  <si>
+    <t>S2+LRI2B</t>
+  </si>
+  <si>
+    <t>500kV AC Yard Bay Interface</t>
+  </si>
+  <si>
+    <t>No. 3</t>
+  </si>
+  <si>
+    <t>No. 4</t>
+  </si>
+  <si>
+    <t>No. 5</t>
+  </si>
+  <si>
+    <t>No. 6</t>
+  </si>
+  <si>
+    <t>S2+ACC1A</t>
+  </si>
+  <si>
+    <t>S2+ACC1B</t>
+  </si>
+  <si>
+    <t>S2+ACC2A</t>
+  </si>
+  <si>
+    <t>S2+ACC2B</t>
+  </si>
+  <si>
+    <t>S2+ACC3A</t>
+  </si>
+  <si>
+    <t>S2+ACC3B</t>
+  </si>
+  <si>
+    <t>S2+ACC4A</t>
+  </si>
+  <si>
+    <t>S2+ACC4B</t>
+  </si>
+  <si>
+    <t>S2+ACC5A</t>
+  </si>
+  <si>
+    <t>S2+ACC5B</t>
+  </si>
+  <si>
+    <t>S2+ACC6A</t>
+  </si>
+  <si>
+    <t>S2+ACC6B</t>
+  </si>
+  <si>
+    <t>AC Filter Interface</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>S2+AFC1A1</t>
+  </si>
+  <si>
+    <t>S2+AFC1A2</t>
+  </si>
+  <si>
+    <t>S2+AFC1B1</t>
+  </si>
+  <si>
+    <t>S2+AFC1B2</t>
+  </si>
+  <si>
+    <t>S2+AFC2A1</t>
+  </si>
+  <si>
+    <t>S2+AFC2A2</t>
+  </si>
+  <si>
+    <t>S2+AFC2B1</t>
+  </si>
+  <si>
+    <t>S2+AFC2B2</t>
+  </si>
+  <si>
+    <t>S2+AFC3A1</t>
+  </si>
+  <si>
+    <t>S2+AFC3A2</t>
+  </si>
+  <si>
+    <t>S2+AFC3B1</t>
+  </si>
+  <si>
+    <t>S2+AFC3B2</t>
+  </si>
+  <si>
+    <t>S2+AFC4A1</t>
+  </si>
+  <si>
+    <t>S2+AFC4A2</t>
+  </si>
+  <si>
+    <t>S2+AFC4B1</t>
+  </si>
+  <si>
+    <t>S2+AFC4B2</t>
+  </si>
+  <si>
+    <t>S2+FMPI1A</t>
+  </si>
+  <si>
+    <t>S2+FMPI1B</t>
+  </si>
+  <si>
+    <t>S2+FMPI2A</t>
+  </si>
+  <si>
+    <t>S2+FMPI3A</t>
+  </si>
+  <si>
+    <t>S2+FMPI4A</t>
+  </si>
+  <si>
+    <t>S2+FMPI2B</t>
+  </si>
+  <si>
+    <t>S2+FMPI3B</t>
+  </si>
+  <si>
+    <t>S2+FMPI4B</t>
+  </si>
+  <si>
+    <t>AC Filter Protection Measuring Interface</t>
+  </si>
+  <si>
+    <t>AC Filter Start Measuring Interface</t>
+  </si>
+  <si>
+    <t>S2+FMTI1A</t>
+  </si>
+  <si>
+    <t>S2+FMTI1B</t>
+  </si>
+  <si>
+    <t>S2+FMTI2A</t>
+  </si>
+  <si>
+    <t>S2+FMTI2B</t>
+  </si>
+  <si>
+    <t>S2+FMTI3A</t>
+  </si>
+  <si>
+    <t>S2+FMTI3B</t>
+  </si>
+  <si>
+    <t>S2+FMTI4A</t>
+  </si>
+  <si>
+    <t>S2+FMTI4B</t>
+  </si>
+  <si>
+    <t>AC Filter Operate Box</t>
+  </si>
+  <si>
+    <t>S2+AFI1-12</t>
+  </si>
+  <si>
+    <t>S2+AFI1-34</t>
+  </si>
+  <si>
+    <t>S2+AFI2-12</t>
+  </si>
+  <si>
+    <t>S2+AFI2-34</t>
+  </si>
+  <si>
+    <t>S2+AFI3-12</t>
+  </si>
+  <si>
+    <t>S2+AFI3-34</t>
+  </si>
+  <si>
+    <t>S2+AFI4-12</t>
+  </si>
+  <si>
+    <t>S2+AFI4-34</t>
+  </si>
+  <si>
+    <t>AC Filter Protection</t>
+  </si>
+  <si>
+    <t>S2+AFP1A</t>
+  </si>
+  <si>
+    <t>S2+AFP1B</t>
+  </si>
+  <si>
+    <t>S2+AFP2A</t>
+  </si>
+  <si>
+    <t>S2+AFP2B</t>
+  </si>
+  <si>
+    <t>S2+AFP3A</t>
+  </si>
+  <si>
+    <t>S2+AFP3B</t>
+  </si>
+  <si>
+    <t>S2+AFP4A</t>
+  </si>
+  <si>
+    <t>S2+AFP4B</t>
+  </si>
+  <si>
+    <t>AC Station Control</t>
+  </si>
+  <si>
+    <t>S2+ASCA</t>
+  </si>
+  <si>
+    <t>S2+ASCB</t>
+  </si>
+  <si>
+    <t>S2+ACI1</t>
+  </si>
+  <si>
+    <t>S2+ACI2</t>
+  </si>
+  <si>
+    <t>S2+ACI3</t>
+  </si>
+  <si>
+    <t>AC Station Interface</t>
+  </si>
+  <si>
+    <t>S2+ACI52A</t>
+  </si>
+  <si>
+    <t>S2+ACI52B</t>
+  </si>
+  <si>
+    <t>AC Station Interface 52</t>
+  </si>
+  <si>
+    <t>S2+AWS</t>
+  </si>
+  <si>
+    <t>Auxiliary System Interface</t>
+  </si>
+  <si>
+    <t>S2+COMA</t>
+  </si>
+  <si>
+    <t>S2+COMB</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>S2+ITFP1A</t>
+  </si>
+  <si>
+    <t>S2+ITFP1B</t>
+  </si>
+  <si>
+    <t>S2+ITFP1C</t>
+  </si>
+  <si>
+    <t>S2+ITFP2A</t>
+  </si>
+  <si>
+    <t>S2+ITFP2B</t>
+  </si>
+  <si>
+    <t>S2+ITFP2C</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Pole 1</t>
+  </si>
+  <si>
+    <t>Pole 2</t>
+  </si>
+  <si>
+    <t>Pole Converter Transformer Non-electric value Interface</t>
+  </si>
+  <si>
+    <t>S1+TSIM</t>
+  </si>
+  <si>
+    <t>S2+TSIM</t>
+  </si>
+  <si>
+    <t>Station Control System Simulator</t>
+  </si>
+  <si>
+    <t>Station 1</t>
+  </si>
+  <si>
+    <t>Station 2</t>
+  </si>
+  <si>
+    <t>S2+TFDI1A</t>
+  </si>
+  <si>
+    <t>S2+TFDI1B</t>
+  </si>
+  <si>
+    <t>S2+TFDI2A</t>
+  </si>
+  <si>
+    <t>S2+TFDI2B</t>
+  </si>
+  <si>
+    <t>S2+TFYI1A</t>
+  </si>
+  <si>
+    <t>S2+TFYI1B</t>
+  </si>
+  <si>
+    <t>S2+TFYI2A</t>
+  </si>
+  <si>
+    <t>S2+TFYI2B</t>
+  </si>
+  <si>
+    <t>Pole 1 YD</t>
+  </si>
+  <si>
+    <t>Pole 2 YD</t>
+  </si>
+  <si>
+    <t>Pole 1 YY</t>
+  </si>
+  <si>
+    <t>Pole 2 YY</t>
+  </si>
+  <si>
+    <t>Pole Converter Transformer Interface</t>
+  </si>
+  <si>
+    <t>S2+TFP1A</t>
+  </si>
+  <si>
+    <t>S2+TFP1B</t>
+  </si>
+  <si>
+    <t>S2+TFP1C</t>
+  </si>
+  <si>
+    <t>S2+TFP2A</t>
+  </si>
+  <si>
+    <t>S2+TFP2B</t>
+  </si>
+  <si>
+    <t>S2+TFP2C</t>
+  </si>
+  <si>
+    <t>Pole Converter Transformer Protection</t>
+  </si>
+  <si>
+    <t>S2+LFL1</t>
+  </si>
+  <si>
+    <t>S2+LFL2</t>
+  </si>
+  <si>
+    <t>DC Line Fault Locator</t>
+  </si>
+  <si>
+    <t>S2+DSCA</t>
+  </si>
+  <si>
+    <t>S2+DSCB</t>
+  </si>
+  <si>
+    <t>DC Station Control</t>
+  </si>
+  <si>
+    <t>S2+DCI</t>
+  </si>
+  <si>
+    <t>DC Station Interface</t>
+  </si>
+  <si>
+    <t>S2+BSIA</t>
+  </si>
+  <si>
+    <t>S2+BSIB</t>
+  </si>
+  <si>
+    <t>Bipole DC Yard Interface</t>
+  </si>
+  <si>
+    <t>S2+PSI1A</t>
+  </si>
+  <si>
+    <t>S2+PSI1B</t>
+  </si>
+  <si>
+    <t>S2+PSI2A</t>
+  </si>
+  <si>
+    <t>S2+PSI2B</t>
+  </si>
+  <si>
+    <t>Pole DC Yard Interface</t>
+  </si>
+  <si>
+    <t>S2+ELIS</t>
+  </si>
+  <si>
+    <t>Electrode Line Monitoring</t>
+  </si>
+  <si>
+    <t>S2+ELCI</t>
+  </si>
+  <si>
+    <t>Local Box for Electrode Line Monitoring</t>
+  </si>
+  <si>
+    <t>S2+OFI</t>
+  </si>
+  <si>
+    <t>S2+OFI1</t>
+  </si>
+  <si>
+    <t>S2+OFI2</t>
+  </si>
+  <si>
+    <t>S2+OFI3</t>
+  </si>
+  <si>
+    <t>FO Cable Interface</t>
+  </si>
+  <si>
+    <t>S2+OHM</t>
+  </si>
+  <si>
+    <t>Harmonic Monitoring</t>
+  </si>
+  <si>
+    <t>S2+APT1A</t>
+  </si>
+  <si>
+    <t>S2+APT1B</t>
+  </si>
+  <si>
+    <t>S2+APT2A</t>
+  </si>
+  <si>
+    <t>S2+APT2B</t>
+  </si>
+  <si>
+    <t>HV Transformer Interface</t>
+  </si>
+  <si>
+    <t>S2+LWS</t>
+  </si>
+  <si>
+    <t>Local Control Interface</t>
+  </si>
+  <si>
+    <t>S2+BMI1</t>
+  </si>
+  <si>
+    <t>S2+BMI2</t>
+  </si>
+  <si>
+    <t>Bipole Merging Unit</t>
+  </si>
+  <si>
+    <t>Pole Merging Unit</t>
+  </si>
+  <si>
+    <t>S2+EMI1</t>
+  </si>
+  <si>
+    <t>S2+EMI2</t>
+  </si>
+  <si>
+    <t>S2+HCBT</t>
+  </si>
+  <si>
+    <t>Offline Board Test Cubicle</t>
+  </si>
+  <si>
+    <t>S2+PCP1A</t>
+  </si>
+  <si>
+    <t>S2+PCP1B</t>
+  </si>
+  <si>
+    <t>S2+PCP2A</t>
+  </si>
+  <si>
+    <t>S2+PCP2B</t>
+  </si>
+  <si>
+    <t>Pole Control</t>
+  </si>
+  <si>
+    <t>S2+PCI</t>
+  </si>
+  <si>
+    <t>Pole Control Interface</t>
+  </si>
+  <si>
+    <t>Pole Measuring Interface</t>
+  </si>
+  <si>
+    <t>S2+PMI1A</t>
+  </si>
+  <si>
+    <t>S2+PMI1B</t>
+  </si>
+  <si>
+    <t>S2+PMI1C</t>
+  </si>
+  <si>
+    <t>S2+PMI2A</t>
+  </si>
+  <si>
+    <t>S2+PMI2B</t>
+  </si>
+  <si>
+    <t>S2+PMI2C</t>
+  </si>
+  <si>
+    <t>Pole Protection</t>
+  </si>
+  <si>
+    <t>S2+PPR1A</t>
+  </si>
+  <si>
+    <t>S2+PPR1B</t>
+  </si>
+  <si>
+    <t>S2+PPR1C</t>
+  </si>
+  <si>
+    <t>S2+PPR2A</t>
+  </si>
+  <si>
+    <t>S2+PPR2B</t>
+  </si>
+  <si>
+    <t>S2+PPR2C</t>
+  </si>
+  <si>
+    <t>S2+GWS</t>
+  </si>
+  <si>
+    <t>Remote Control Communication</t>
+  </si>
+  <si>
+    <t>S2+SER1</t>
+  </si>
+  <si>
+    <t>S2+SER2</t>
+  </si>
+  <si>
+    <t>Pole SER Interface</t>
+  </si>
+  <si>
+    <t>S2+SCM</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>S2+SPCA</t>
+  </si>
+  <si>
+    <t>S2+SPCB</t>
+  </si>
+  <si>
+    <t>Station Power Control</t>
+  </si>
+  <si>
+    <t>S2+SPI1A</t>
+  </si>
+  <si>
+    <t>S2+SPI1B</t>
+  </si>
+  <si>
+    <t>10kV I Station Service Interface</t>
+  </si>
+  <si>
+    <t>10kV II Station Service Interface</t>
+  </si>
+  <si>
+    <t>S2+SPI2A</t>
+  </si>
+  <si>
+    <t>S2+SPI2B</t>
+  </si>
+  <si>
+    <t>S2+SPI3A</t>
+  </si>
+  <si>
+    <t>S2+SPI3B</t>
+  </si>
+  <si>
+    <t>Incoming Station Service Interface 1</t>
+  </si>
+  <si>
+    <t>Incoming Station Service Interface 2</t>
+  </si>
+  <si>
+    <t>400V Station Service Interface</t>
+  </si>
+  <si>
+    <t>S2+SPI5A</t>
+  </si>
+  <si>
+    <t>S2+SPI5B</t>
+  </si>
+  <si>
+    <t>Diesel Generator Interface</t>
+  </si>
+  <si>
+    <t>S2+SPI6A</t>
+  </si>
+  <si>
+    <t>S2+SPI6B</t>
+  </si>
+  <si>
+    <t>Pole 1 Station Service Interface</t>
+  </si>
+  <si>
+    <t>S2+SPI11A</t>
+  </si>
+  <si>
+    <t>S2+SPI11B</t>
+  </si>
+  <si>
+    <t>Pole 2 Station Service Interface</t>
+  </si>
+  <si>
+    <t>S2+SPI21A</t>
+  </si>
+  <si>
+    <t>S2+SPI21B</t>
+  </si>
+  <si>
+    <t>S2+VFI 1</t>
+  </si>
+  <si>
+    <t>S2+VFI 2</t>
+  </si>
+  <si>
+    <t>Valve Hall Fire Trip Interface</t>
+  </si>
+  <si>
+    <t>Pole Valve Hall Interface</t>
+  </si>
+  <si>
+    <t>S2+VHI1A</t>
+  </si>
+  <si>
+    <t>S2+VHI1B</t>
+  </si>
+  <si>
+    <t>S2+VHI2A</t>
+  </si>
+  <si>
+    <t>S2+VHI2B</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -32,7 +745,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -40,18 +753,212 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -98,7 +1005,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -133,7 +1040,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -341,10 +1248,1928 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:FV21"/>
+  <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="20.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="4"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU2" s="4"/>
+      <c r="AV2" s="4"/>
+      <c r="AW2" s="4"/>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="AZ2" s="4"/>
+      <c r="BA2" s="5"/>
+      <c r="BB2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BC2" s="4"/>
+      <c r="BD2" s="4"/>
+      <c r="BE2" s="4"/>
+      <c r="BF2" s="4"/>
+      <c r="BG2" s="4"/>
+      <c r="BH2" s="4"/>
+      <c r="BI2" s="5"/>
+      <c r="BJ2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BK2" s="4"/>
+      <c r="BL2" s="4"/>
+      <c r="BM2" s="4"/>
+      <c r="BN2" s="4"/>
+      <c r="BO2" s="4"/>
+      <c r="BP2" s="4"/>
+      <c r="BQ2" s="5"/>
+      <c r="BR2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS2" s="5"/>
+      <c r="BT2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BU2" s="4"/>
+      <c r="BV2" s="5"/>
+      <c r="BW2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BX2" s="5"/>
+      <c r="BY2" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="BZ2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="CA2" s="5"/>
+      <c r="CB2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="CC2" s="4"/>
+      <c r="CD2" s="4"/>
+      <c r="CE2" s="4"/>
+      <c r="CF2" s="4"/>
+      <c r="CG2" s="5"/>
+      <c r="CH2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="CI2" s="5"/>
+      <c r="CJ2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CK2" s="4"/>
+      <c r="CL2" s="4"/>
+      <c r="CM2" s="4"/>
+      <c r="CN2" s="4"/>
+      <c r="CO2" s="4"/>
+      <c r="CP2" s="4"/>
+      <c r="CQ2" s="5"/>
+      <c r="CR2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CS2" s="4"/>
+      <c r="CT2" s="4"/>
+      <c r="CU2" s="4"/>
+      <c r="CV2" s="4"/>
+      <c r="CW2" s="5"/>
+      <c r="CX2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="CY2" s="5"/>
+      <c r="CZ2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DA2" s="5"/>
+      <c r="DB2" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="DC2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="DD2" s="5"/>
+      <c r="DE2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="DF2" s="4"/>
+      <c r="DG2" s="4"/>
+      <c r="DH2" s="5"/>
+      <c r="DI2" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="DJ2" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="DK2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="DL2" s="4"/>
+      <c r="DM2" s="4"/>
+      <c r="DN2" s="5"/>
+      <c r="DO2" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="DP2" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="DQ2" s="4"/>
+      <c r="DR2" s="4"/>
+      <c r="DS2" s="5"/>
+      <c r="DT2" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="DU2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="DV2" s="5"/>
+      <c r="DW2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="DX2" s="5"/>
+      <c r="DY2" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="DZ2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="EA2" s="4"/>
+      <c r="EB2" s="4"/>
+      <c r="EC2" s="5"/>
+      <c r="ED2" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="EE2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="EF2" s="4"/>
+      <c r="EG2" s="4"/>
+      <c r="EH2" s="5"/>
+      <c r="EI2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="EJ2" s="4"/>
+      <c r="EK2" s="4"/>
+      <c r="EL2" s="4"/>
+      <c r="EM2" s="4"/>
+      <c r="EN2" s="5"/>
+      <c r="EO2" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="EP2" s="4"/>
+      <c r="EQ2" s="4"/>
+      <c r="ER2" s="4"/>
+      <c r="ES2" s="4"/>
+      <c r="ET2" s="5"/>
+      <c r="EU2" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="EV2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="EW2" s="5"/>
+      <c r="EX2" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="EY2" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="EZ2" s="5"/>
+      <c r="FA2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="FB2" s="5"/>
+      <c r="FC2" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="FD2" s="5"/>
+      <c r="FE2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="FF2" s="5"/>
+      <c r="FG2" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FH2" s="5"/>
+      <c r="FI2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="FJ2" s="5"/>
+      <c r="FK2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="FL2" s="5"/>
+      <c r="FM2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="FN2" s="5"/>
+      <c r="FO2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="FP2" s="5"/>
+      <c r="FQ2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="FR2" s="5"/>
+      <c r="FS2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="FT2" s="4"/>
+      <c r="FU2" s="4"/>
+      <c r="FV2" s="5"/>
+    </row>
+    <row r="3" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="8"/>
+      <c r="V3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="7"/>
+      <c r="AP3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AU3" s="7"/>
+      <c r="AV3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="7"/>
+      <c r="AZ3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA3" s="8"/>
+      <c r="BB3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="BC3" s="7"/>
+      <c r="BD3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE3" s="7"/>
+      <c r="BF3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BG3" s="7"/>
+      <c r="BH3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="7"/>
+      <c r="BL3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM3" s="7"/>
+      <c r="BN3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO3" s="7"/>
+      <c r="BP3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="BQ3" s="8"/>
+      <c r="BR3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BT3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="BU3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="BX3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BY3" s="22"/>
+      <c r="BZ3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="CB3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="CC3" s="7"/>
+      <c r="CD3" s="7"/>
+      <c r="CE3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="CF3" s="7"/>
+      <c r="CG3" s="8"/>
+      <c r="CH3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="CI3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="CJ3" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="CK3" s="7"/>
+      <c r="CL3" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="CM3" s="7"/>
+      <c r="CN3" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" s="7"/>
+      <c r="CP3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="CQ3" s="8"/>
+      <c r="CR3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="CS3" s="7"/>
+      <c r="CT3" s="7"/>
+      <c r="CU3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="CV3" s="7"/>
+      <c r="CW3" s="8"/>
+      <c r="CX3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="CY3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CZ3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="DA3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="DB3" s="22"/>
+      <c r="DC3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="DD3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="DE3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="DF3" s="7"/>
+      <c r="DG3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="DH3" s="8"/>
+      <c r="DI3" s="22"/>
+      <c r="DJ3" s="22"/>
+      <c r="DK3" s="6"/>
+      <c r="DL3" s="7"/>
+      <c r="DM3" s="7"/>
+      <c r="DN3" s="8"/>
+      <c r="DO3" s="22"/>
+      <c r="DP3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="DQ3" s="7"/>
+      <c r="DR3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="DS3" s="8"/>
+      <c r="DT3" s="22"/>
+      <c r="DU3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="DV3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="DW3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="DX3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="DY3" s="22"/>
+      <c r="DZ3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="EA3" s="7"/>
+      <c r="EB3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="EC3" s="8"/>
+      <c r="ED3" s="22"/>
+      <c r="EE3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="EF3" s="7"/>
+      <c r="EG3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="EH3" s="8"/>
+      <c r="EI3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="EJ3" s="7"/>
+      <c r="EK3" s="7"/>
+      <c r="EL3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="EM3" s="7"/>
+      <c r="EN3" s="8"/>
+      <c r="EO3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="EP3" s="7"/>
+      <c r="EQ3" s="7"/>
+      <c r="ER3" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="ES3" s="7"/>
+      <c r="ET3" s="8"/>
+      <c r="EU3" s="22"/>
+      <c r="EV3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="EW3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="EX3" s="22"/>
+      <c r="EY3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="EZ3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FA3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FB3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FC3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FD3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FE3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FF3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FG3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FH3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FI3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FJ3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FK3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FL3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FM3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FN3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FO3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FP3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="FQ3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="FR3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="FS3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="FT3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="FU3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV3" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="BK4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BO4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BQ4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR4" s="6"/>
+      <c r="BS4" s="8"/>
+      <c r="BT4" s="6"/>
+      <c r="BU4" s="7"/>
+      <c r="BV4" s="8"/>
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="8"/>
+      <c r="BY4" s="22"/>
+      <c r="BZ4" s="6"/>
+      <c r="CA4" s="8"/>
+      <c r="CB4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="CC4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CD4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="CE4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="CF4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CG4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="CH4" s="6"/>
+      <c r="CI4" s="8"/>
+      <c r="CJ4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="CK4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CN4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="CO4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CP4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="CQ4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="CR4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="CS4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CT4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="CU4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="CV4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="CX4" s="6"/>
+      <c r="CY4" s="8"/>
+      <c r="CZ4" s="6"/>
+      <c r="DA4" s="8"/>
+      <c r="DB4" s="22"/>
+      <c r="DC4" s="6"/>
+      <c r="DD4" s="8"/>
+      <c r="DE4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="DF4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="DG4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="DH4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="DI4" s="22"/>
+      <c r="DJ4" s="22"/>
+      <c r="DK4" s="6"/>
+      <c r="DL4" s="7"/>
+      <c r="DM4" s="7"/>
+      <c r="DN4" s="8"/>
+      <c r="DO4" s="22"/>
+      <c r="DP4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="DQ4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="DR4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="DS4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="DT4" s="22"/>
+      <c r="DU4" s="6"/>
+      <c r="DV4" s="8"/>
+      <c r="DW4" s="6"/>
+      <c r="DX4" s="8"/>
+      <c r="DY4" s="22"/>
+      <c r="DZ4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="EA4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="EB4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="EC4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="ED4" s="22"/>
+      <c r="EE4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="EF4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="EG4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="EH4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="EI4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="EJ4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="EK4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="EL4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="EM4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="EN4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="EO4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="EP4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="EQ4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="ER4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="ES4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="ET4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="EU4" s="22"/>
+      <c r="EV4" s="6"/>
+      <c r="EW4" s="8"/>
+      <c r="EX4" s="22"/>
+      <c r="EY4" s="6"/>
+      <c r="EZ4" s="8"/>
+      <c r="FA4" s="6"/>
+      <c r="FB4" s="8"/>
+      <c r="FC4" s="6"/>
+      <c r="FD4" s="8"/>
+      <c r="FE4" s="6"/>
+      <c r="FF4" s="8"/>
+      <c r="FG4" s="6"/>
+      <c r="FH4" s="8"/>
+      <c r="FI4" s="6"/>
+      <c r="FJ4" s="8"/>
+      <c r="FK4" s="6"/>
+      <c r="FL4" s="8"/>
+      <c r="FM4" s="6"/>
+      <c r="FN4" s="8"/>
+      <c r="FO4" s="6"/>
+      <c r="FP4" s="8"/>
+      <c r="FQ4" s="6"/>
+      <c r="FR4" s="8"/>
+      <c r="FS4" s="6"/>
+      <c r="FT4" s="7"/>
+      <c r="FU4" s="7"/>
+      <c r="FV4" s="8"/>
+    </row>
+    <row r="5" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ5" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV5" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AW5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX5" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AZ5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB5" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="BC5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="BD5" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="BE5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="BF5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BG5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="BH5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL5" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM5" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="BN5" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BO5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP5" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="BQ5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="BR5" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="BS5" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="BT5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="BU5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="BW5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="BX5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="BY5" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="BZ5" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="CA5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="CB5" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="CC5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="CD5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="CE5" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="CF5" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="CG5" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="CH5" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="CI5" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="CJ5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="CK5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="CL5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="CM5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="CN5" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="CO5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="CP5" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="CQ5" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="CR5" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="CS5" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="CT5" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU5" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="CV5" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="CW5" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX5" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="CY5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="CZ5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="DA5" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="DC5" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="DD5" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="DE5" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="DF5" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="DG5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="DH5" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="DI5" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="DJ5" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="DK5" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="DL5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="DM5" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="DN5" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="DO5" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="DP5" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="DQ5" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="DR5" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="DS5" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="DT5" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="DU5" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="DV5" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="DW5" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="DX5" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="DY5" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="DZ5" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="EA5" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="EB5" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="EC5" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="ED5" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="EE5" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="EF5" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="EG5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="EH5" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="EI5" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ5" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="EK5" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="EL5" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="EM5" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="EN5" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="EO5" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="EP5" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="EQ5" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="ER5" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="ES5" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="ET5" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="EU5" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="EV5" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="EW5" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="EX5" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="EY5" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="EZ5" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="FA5" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="FB5" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="FC5" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="FD5" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="FE5" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="FF5" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="FG5" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="FH5" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="FI5" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="FJ5" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="FK5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="FL5" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="FM5" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="FN5" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="FO5" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="FP5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="FQ5" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="FR5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="FS5" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="FT5" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="FU5" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="FV5" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM9" s="1"/>
+      <c r="CN9" s="1"/>
+    </row>
+    <row r="10" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6"/>
+      <c r="C12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6"/>
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6"/>
+      <c r="C18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6"/>
+      <c r="C20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="156">
+    <mergeCell ref="FS3:FS4"/>
+    <mergeCell ref="FT3:FT4"/>
+    <mergeCell ref="FU3:FU4"/>
+    <mergeCell ref="FV3:FV4"/>
+    <mergeCell ref="FS2:FV2"/>
+    <mergeCell ref="FO2:FP2"/>
+    <mergeCell ref="FO3:FO4"/>
+    <mergeCell ref="FP3:FP4"/>
+    <mergeCell ref="FQ2:FR2"/>
+    <mergeCell ref="FQ3:FQ4"/>
+    <mergeCell ref="FR3:FR4"/>
+    <mergeCell ref="FK2:FL2"/>
+    <mergeCell ref="FK3:FK4"/>
+    <mergeCell ref="FL3:FL4"/>
+    <mergeCell ref="FM2:FN2"/>
+    <mergeCell ref="FM3:FM4"/>
+    <mergeCell ref="FN3:FN4"/>
+    <mergeCell ref="FG2:FH2"/>
+    <mergeCell ref="FG3:FG4"/>
+    <mergeCell ref="FH3:FH4"/>
+    <mergeCell ref="FI2:FJ2"/>
+    <mergeCell ref="FI3:FI4"/>
+    <mergeCell ref="FJ3:FJ4"/>
+    <mergeCell ref="FC2:FD2"/>
+    <mergeCell ref="FC3:FC4"/>
+    <mergeCell ref="FD3:FD4"/>
+    <mergeCell ref="FE2:FF2"/>
+    <mergeCell ref="FE3:FE4"/>
+    <mergeCell ref="FF3:FF4"/>
+    <mergeCell ref="EX2:EX4"/>
+    <mergeCell ref="EY2:EZ2"/>
+    <mergeCell ref="EY3:EY4"/>
+    <mergeCell ref="EZ3:EZ4"/>
+    <mergeCell ref="FA2:FB2"/>
+    <mergeCell ref="FA3:FA4"/>
+    <mergeCell ref="FB3:FB4"/>
+    <mergeCell ref="EO2:ET2"/>
+    <mergeCell ref="EO3:EQ3"/>
+    <mergeCell ref="ER3:ET3"/>
+    <mergeCell ref="EU2:EU4"/>
+    <mergeCell ref="EV3:EV4"/>
+    <mergeCell ref="EW3:EW4"/>
+    <mergeCell ref="EV2:EW2"/>
+    <mergeCell ref="ED2:ED4"/>
+    <mergeCell ref="EE2:EH2"/>
+    <mergeCell ref="EE3:EF3"/>
+    <mergeCell ref="EG3:EH3"/>
+    <mergeCell ref="EI2:EN2"/>
+    <mergeCell ref="EI3:EK3"/>
+    <mergeCell ref="EL3:EN3"/>
+    <mergeCell ref="DW2:DX2"/>
+    <mergeCell ref="DW3:DW4"/>
+    <mergeCell ref="DX3:DX4"/>
+    <mergeCell ref="DY2:DY4"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="DZ2:EC2"/>
+    <mergeCell ref="DO2:DO4"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DP2:DS2"/>
+    <mergeCell ref="DT2:DT4"/>
+    <mergeCell ref="DU2:DV2"/>
+    <mergeCell ref="DU3:DU4"/>
+    <mergeCell ref="DV3:DV4"/>
+    <mergeCell ref="DE3:DF3"/>
+    <mergeCell ref="DG3:DH3"/>
+    <mergeCell ref="DE2:DH2"/>
+    <mergeCell ref="DI2:DI4"/>
+    <mergeCell ref="DJ2:DJ4"/>
+    <mergeCell ref="DK2:DN4"/>
+    <mergeCell ref="CZ3:CZ4"/>
+    <mergeCell ref="DA3:DA4"/>
+    <mergeCell ref="CZ2:DA2"/>
+    <mergeCell ref="DB2:DB4"/>
+    <mergeCell ref="DC2:DD2"/>
+    <mergeCell ref="DC3:DC4"/>
+    <mergeCell ref="DD3:DD4"/>
+    <mergeCell ref="CR3:CT3"/>
+    <mergeCell ref="CU3:CW3"/>
+    <mergeCell ref="CR2:CW2"/>
+    <mergeCell ref="CX3:CX4"/>
+    <mergeCell ref="CY3:CY4"/>
+    <mergeCell ref="CX2:CY2"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="CJ2:CQ2"/>
+    <mergeCell ref="CM9:CN9"/>
+    <mergeCell ref="CB3:CD3"/>
+    <mergeCell ref="CE3:CG3"/>
+    <mergeCell ref="CB2:CG2"/>
+    <mergeCell ref="CH3:CH4"/>
+    <mergeCell ref="CI3:CI4"/>
+    <mergeCell ref="CH2:CI2"/>
+    <mergeCell ref="BW3:BW4"/>
+    <mergeCell ref="BX3:BX4"/>
+    <mergeCell ref="BW2:BX2"/>
+    <mergeCell ref="BY2:BY4"/>
+    <mergeCell ref="BZ3:BZ4"/>
+    <mergeCell ref="CA3:CA4"/>
+    <mergeCell ref="BZ2:CA2"/>
+    <mergeCell ref="BR2:BS2"/>
+    <mergeCell ref="BR3:BR4"/>
+    <mergeCell ref="BS3:BS4"/>
+    <mergeCell ref="BT3:BT4"/>
+    <mergeCell ref="BU3:BU4"/>
+    <mergeCell ref="BV3:BV4"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BB2:BI2"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BJ2:BQ2"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="AL2:AS2"/>
+    <mergeCell ref="AT2:BA2"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="V2:AK2"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="B10:B21"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B2:E5"/>
+    <mergeCell ref="C6:C7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/HVDC Converter Station/Connections.xlsx
+++ b/HVDC Converter Station/Connections.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="236">
   <si>
     <t>35kV Reactor Interface</t>
   </si>
@@ -745,7 +745,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -870,34 +870,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -924,9 +940,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -936,13 +949,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1249,1873 +1301,3656 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:FV21"/>
-  <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:FV178"/>
+  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="20.7109375" style="2"/>
+    <col min="1" max="16384" width="15.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="3" t="s">
+    <row r="2" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="3" t="s">
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="3" t="s">
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="3" t="s">
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
-      <c r="AO2" s="4"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="4"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="3" t="s">
+      <c r="AM2" s="18"/>
+      <c r="AN2" s="18"/>
+      <c r="AO2" s="18"/>
+      <c r="AP2" s="18"/>
+      <c r="AQ2" s="18"/>
+      <c r="AR2" s="18"/>
+      <c r="AS2" s="19"/>
+      <c r="AT2" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="AU2" s="4"/>
-      <c r="AV2" s="4"/>
-      <c r="AW2" s="4"/>
-      <c r="AX2" s="4"/>
-      <c r="AY2" s="4"/>
-      <c r="AZ2" s="4"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="3" t="s">
+      <c r="AU2" s="18"/>
+      <c r="AV2" s="18"/>
+      <c r="AW2" s="18"/>
+      <c r="AX2" s="18"/>
+      <c r="AY2" s="18"/>
+      <c r="AZ2" s="18"/>
+      <c r="BA2" s="19"/>
+      <c r="BB2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="BC2" s="4"/>
-      <c r="BD2" s="4"/>
-      <c r="BE2" s="4"/>
-      <c r="BF2" s="4"/>
-      <c r="BG2" s="4"/>
-      <c r="BH2" s="4"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="3" t="s">
+      <c r="BC2" s="18"/>
+      <c r="BD2" s="18"/>
+      <c r="BE2" s="18"/>
+      <c r="BF2" s="18"/>
+      <c r="BG2" s="18"/>
+      <c r="BH2" s="18"/>
+      <c r="BI2" s="19"/>
+      <c r="BJ2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="BK2" s="4"/>
-      <c r="BL2" s="4"/>
-      <c r="BM2" s="4"/>
-      <c r="BN2" s="4"/>
-      <c r="BO2" s="4"/>
-      <c r="BP2" s="4"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="3" t="s">
+      <c r="BK2" s="18"/>
+      <c r="BL2" s="18"/>
+      <c r="BM2" s="18"/>
+      <c r="BN2" s="18"/>
+      <c r="BO2" s="18"/>
+      <c r="BP2" s="18"/>
+      <c r="BQ2" s="19"/>
+      <c r="BR2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="3" t="s">
+      <c r="BS2" s="19"/>
+      <c r="BT2" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="BU2" s="4"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="3" t="s">
+      <c r="BU2" s="18"/>
+      <c r="BV2" s="19"/>
+      <c r="BW2" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="21" t="s">
+      <c r="BX2" s="19"/>
+      <c r="BY2" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="BZ2" s="3" t="s">
+      <c r="BZ2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="3" t="s">
+      <c r="CA2" s="19"/>
+      <c r="CB2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="CC2" s="4"/>
-      <c r="CD2" s="4"/>
-      <c r="CE2" s="4"/>
-      <c r="CF2" s="4"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="3" t="s">
+      <c r="CC2" s="18"/>
+      <c r="CD2" s="18"/>
+      <c r="CE2" s="18"/>
+      <c r="CF2" s="18"/>
+      <c r="CG2" s="19"/>
+      <c r="CH2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="3" t="s">
+      <c r="CI2" s="19"/>
+      <c r="CJ2" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="CK2" s="4"/>
-      <c r="CL2" s="4"/>
-      <c r="CM2" s="4"/>
-      <c r="CN2" s="4"/>
-      <c r="CO2" s="4"/>
-      <c r="CP2" s="4"/>
-      <c r="CQ2" s="5"/>
-      <c r="CR2" s="3" t="s">
+      <c r="CK2" s="18"/>
+      <c r="CL2" s="18"/>
+      <c r="CM2" s="18"/>
+      <c r="CN2" s="18"/>
+      <c r="CO2" s="18"/>
+      <c r="CP2" s="18"/>
+      <c r="CQ2" s="19"/>
+      <c r="CR2" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="CS2" s="4"/>
-      <c r="CT2" s="4"/>
-      <c r="CU2" s="4"/>
-      <c r="CV2" s="4"/>
-      <c r="CW2" s="5"/>
-      <c r="CX2" s="3" t="s">
+      <c r="CS2" s="18"/>
+      <c r="CT2" s="18"/>
+      <c r="CU2" s="18"/>
+      <c r="CV2" s="18"/>
+      <c r="CW2" s="19"/>
+      <c r="CX2" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="CY2" s="5"/>
-      <c r="CZ2" s="3" t="s">
+      <c r="CY2" s="19"/>
+      <c r="CZ2" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="DA2" s="5"/>
-      <c r="DB2" s="21" t="s">
+      <c r="DA2" s="19"/>
+      <c r="DB2" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="DC2" s="3" t="s">
+      <c r="DC2" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="DD2" s="5"/>
-      <c r="DE2" s="3" t="s">
+      <c r="DD2" s="19"/>
+      <c r="DE2" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="DF2" s="4"/>
-      <c r="DG2" s="4"/>
-      <c r="DH2" s="5"/>
-      <c r="DI2" s="21" t="s">
+      <c r="DF2" s="18"/>
+      <c r="DG2" s="18"/>
+      <c r="DH2" s="19"/>
+      <c r="DI2" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="DJ2" s="21" t="s">
+      <c r="DJ2" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="DK2" s="3" t="s">
+      <c r="DK2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="DL2" s="4"/>
-      <c r="DM2" s="4"/>
-      <c r="DN2" s="5"/>
-      <c r="DO2" s="21" t="s">
+      <c r="DL2" s="18"/>
+      <c r="DM2" s="18"/>
+      <c r="DN2" s="19"/>
+      <c r="DO2" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="DP2" s="3" t="s">
+      <c r="DP2" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="DQ2" s="4"/>
-      <c r="DR2" s="4"/>
-      <c r="DS2" s="5"/>
-      <c r="DT2" s="21" t="s">
+      <c r="DQ2" s="18"/>
+      <c r="DR2" s="18"/>
+      <c r="DS2" s="19"/>
+      <c r="DT2" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="DU2" s="3" t="s">
+      <c r="DU2" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="DV2" s="5"/>
-      <c r="DW2" s="3" t="s">
+      <c r="DV2" s="19"/>
+      <c r="DW2" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="DX2" s="5"/>
-      <c r="DY2" s="21" t="s">
+      <c r="DX2" s="19"/>
+      <c r="DY2" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="DZ2" s="3" t="s">
+      <c r="DZ2" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="EA2" s="4"/>
-      <c r="EB2" s="4"/>
-      <c r="EC2" s="5"/>
-      <c r="ED2" s="21" t="s">
+      <c r="EA2" s="18"/>
+      <c r="EB2" s="18"/>
+      <c r="EC2" s="19"/>
+      <c r="ED2" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="EE2" s="3" t="s">
+      <c r="EE2" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="EF2" s="4"/>
-      <c r="EG2" s="4"/>
-      <c r="EH2" s="5"/>
-      <c r="EI2" s="3" t="s">
+      <c r="EF2" s="18"/>
+      <c r="EG2" s="18"/>
+      <c r="EH2" s="19"/>
+      <c r="EI2" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="EJ2" s="4"/>
-      <c r="EK2" s="4"/>
-      <c r="EL2" s="4"/>
-      <c r="EM2" s="4"/>
-      <c r="EN2" s="5"/>
-      <c r="EO2" s="3" t="s">
+      <c r="EJ2" s="18"/>
+      <c r="EK2" s="18"/>
+      <c r="EL2" s="18"/>
+      <c r="EM2" s="18"/>
+      <c r="EN2" s="19"/>
+      <c r="EO2" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="EP2" s="4"/>
-      <c r="EQ2" s="4"/>
-      <c r="ER2" s="4"/>
-      <c r="ES2" s="4"/>
-      <c r="ET2" s="5"/>
-      <c r="EU2" s="21" t="s">
+      <c r="EP2" s="18"/>
+      <c r="EQ2" s="18"/>
+      <c r="ER2" s="18"/>
+      <c r="ES2" s="18"/>
+      <c r="ET2" s="19"/>
+      <c r="EU2" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="EV2" s="3" t="s">
+      <c r="EV2" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="EW2" s="5"/>
-      <c r="EX2" s="21" t="s">
+      <c r="EW2" s="19"/>
+      <c r="EX2" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="EY2" s="3" t="s">
+      <c r="EY2" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="EZ2" s="5"/>
-      <c r="FA2" s="3" t="s">
+      <c r="EZ2" s="19"/>
+      <c r="FA2" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="FB2" s="5"/>
-      <c r="FC2" s="3" t="s">
+      <c r="FB2" s="19"/>
+      <c r="FC2" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="FD2" s="5"/>
-      <c r="FE2" s="3" t="s">
+      <c r="FD2" s="19"/>
+      <c r="FE2" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="FF2" s="5"/>
-      <c r="FG2" s="3" t="s">
+      <c r="FF2" s="19"/>
+      <c r="FG2" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="FH2" s="5"/>
-      <c r="FI2" s="3" t="s">
+      <c r="FH2" s="19"/>
+      <c r="FI2" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="FJ2" s="5"/>
-      <c r="FK2" s="3" t="s">
+      <c r="FJ2" s="19"/>
+      <c r="FK2" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="FL2" s="5"/>
-      <c r="FM2" s="3" t="s">
+      <c r="FL2" s="19"/>
+      <c r="FM2" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="FN2" s="5"/>
-      <c r="FO2" s="3" t="s">
+      <c r="FN2" s="19"/>
+      <c r="FO2" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="FP2" s="5"/>
-      <c r="FQ2" s="3" t="s">
+      <c r="FP2" s="19"/>
+      <c r="FQ2" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="FR2" s="5"/>
-      <c r="FS2" s="3" t="s">
+      <c r="FR2" s="19"/>
+      <c r="FS2" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="FT2" s="4"/>
-      <c r="FU2" s="4"/>
-      <c r="FV2" s="5"/>
-    </row>
-    <row r="3" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6" t="s">
+      <c r="FT2" s="18"/>
+      <c r="FU2" s="18"/>
+      <c r="FV2" s="19"/>
+    </row>
+    <row r="3" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7" t="s">
+      <c r="M3" s="15"/>
+      <c r="N3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7" t="s">
+      <c r="O3" s="15"/>
+      <c r="P3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7" t="s">
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7" t="s">
+      <c r="S3" s="15"/>
+      <c r="T3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="8"/>
-      <c r="V3" s="6" t="s">
+      <c r="U3" s="16"/>
+      <c r="V3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7" t="s">
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7" t="s">
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7" t="s">
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="15"/>
+      <c r="AH3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="6" t="s">
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="AM3" s="7"/>
-      <c r="AN3" s="7" t="s">
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AO3" s="7"/>
-      <c r="AP3" s="7" t="s">
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AQ3" s="7"/>
-      <c r="AR3" s="7" t="s">
+      <c r="AQ3" s="15"/>
+      <c r="AR3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="6" t="s">
+      <c r="AS3" s="16"/>
+      <c r="AT3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="7"/>
-      <c r="AV3" s="7" t="s">
+      <c r="AU3" s="15"/>
+      <c r="AV3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AW3" s="7"/>
-      <c r="AX3" s="7" t="s">
+      <c r="AW3" s="15"/>
+      <c r="AX3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AY3" s="7"/>
-      <c r="AZ3" s="7" t="s">
+      <c r="AY3" s="15"/>
+      <c r="AZ3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="BA3" s="8"/>
-      <c r="BB3" s="6" t="s">
+      <c r="BA3" s="16"/>
+      <c r="BB3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="BC3" s="7"/>
-      <c r="BD3" s="7" t="s">
+      <c r="BC3" s="15"/>
+      <c r="BD3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="BE3" s="7"/>
-      <c r="BF3" s="7" t="s">
+      <c r="BE3" s="15"/>
+      <c r="BF3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="BG3" s="7"/>
-      <c r="BH3" s="7" t="s">
+      <c r="BG3" s="15"/>
+      <c r="BH3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="BI3" s="8"/>
-      <c r="BJ3" s="6" t="s">
+      <c r="BI3" s="16"/>
+      <c r="BJ3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="BK3" s="7"/>
-      <c r="BL3" s="7" t="s">
+      <c r="BK3" s="15"/>
+      <c r="BL3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="BM3" s="7"/>
-      <c r="BN3" s="7" t="s">
+      <c r="BM3" s="15"/>
+      <c r="BN3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="BO3" s="7"/>
-      <c r="BP3" s="7" t="s">
+      <c r="BO3" s="15"/>
+      <c r="BP3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="BQ3" s="8"/>
-      <c r="BR3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="BS3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="BT3" s="6" t="s">
+      <c r="BQ3" s="16"/>
+      <c r="BR3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="BT3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="BU3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="BV3" s="8" t="s">
+      <c r="BV3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BW3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="BX3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="BY3" s="22"/>
-      <c r="BZ3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="CA3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="CB3" s="6" t="s">
+      <c r="BW3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BX3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="BY3" s="21"/>
+      <c r="BZ3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="CA3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="CB3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="CC3" s="7"/>
-      <c r="CD3" s="7"/>
-      <c r="CE3" s="7" t="s">
+      <c r="CC3" s="15"/>
+      <c r="CD3" s="15"/>
+      <c r="CE3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="CF3" s="7"/>
-      <c r="CG3" s="8"/>
-      <c r="CH3" s="6" t="s">
+      <c r="CF3" s="15"/>
+      <c r="CG3" s="16"/>
+      <c r="CH3" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="CI3" s="8" t="s">
+      <c r="CI3" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="CJ3" s="6" t="s">
+      <c r="CJ3" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="CK3" s="7"/>
-      <c r="CL3" s="7" t="s">
+      <c r="CK3" s="15"/>
+      <c r="CL3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="CM3" s="7"/>
-      <c r="CN3" s="7" t="s">
+      <c r="CM3" s="15"/>
+      <c r="CN3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="CO3" s="7"/>
-      <c r="CP3" s="7" t="s">
+      <c r="CO3" s="15"/>
+      <c r="CP3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="CQ3" s="8"/>
-      <c r="CR3" s="6" t="s">
+      <c r="CQ3" s="16"/>
+      <c r="CR3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="CS3" s="7"/>
-      <c r="CT3" s="7"/>
-      <c r="CU3" s="7" t="s">
+      <c r="CS3" s="15"/>
+      <c r="CT3" s="15"/>
+      <c r="CU3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="CV3" s="7"/>
-      <c r="CW3" s="8"/>
-      <c r="CX3" s="6" t="s">
+      <c r="CV3" s="15"/>
+      <c r="CW3" s="16"/>
+      <c r="CX3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="CY3" s="8" t="s">
+      <c r="CY3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="CZ3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="DA3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="DB3" s="22"/>
-      <c r="DC3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="DD3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="DE3" s="6" t="s">
+      <c r="CZ3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="DA3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="DB3" s="21"/>
+      <c r="DC3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="DD3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="DE3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="DF3" s="7"/>
-      <c r="DG3" s="7" t="s">
+      <c r="DF3" s="15"/>
+      <c r="DG3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="DH3" s="8"/>
-      <c r="DI3" s="22"/>
-      <c r="DJ3" s="22"/>
-      <c r="DK3" s="6"/>
-      <c r="DL3" s="7"/>
-      <c r="DM3" s="7"/>
-      <c r="DN3" s="8"/>
-      <c r="DO3" s="22"/>
-      <c r="DP3" s="6" t="s">
+      <c r="DH3" s="16"/>
+      <c r="DI3" s="21"/>
+      <c r="DJ3" s="21"/>
+      <c r="DK3" s="14"/>
+      <c r="DL3" s="15"/>
+      <c r="DM3" s="15"/>
+      <c r="DN3" s="16"/>
+      <c r="DO3" s="21"/>
+      <c r="DP3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="DQ3" s="7"/>
-      <c r="DR3" s="7" t="s">
+      <c r="DQ3" s="15"/>
+      <c r="DR3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="DS3" s="8"/>
-      <c r="DT3" s="22"/>
-      <c r="DU3" s="6" t="s">
+      <c r="DS3" s="16"/>
+      <c r="DT3" s="21"/>
+      <c r="DU3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="DV3" s="8" t="s">
+      <c r="DV3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="DW3" s="6" t="s">
+      <c r="DW3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="DX3" s="8" t="s">
+      <c r="DX3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="DY3" s="22"/>
-      <c r="DZ3" s="6" t="s">
+      <c r="DY3" s="21"/>
+      <c r="DZ3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="EA3" s="7"/>
-      <c r="EB3" s="7" t="s">
+      <c r="EA3" s="15"/>
+      <c r="EB3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="EC3" s="8"/>
-      <c r="ED3" s="22"/>
-      <c r="EE3" s="6" t="s">
+      <c r="EC3" s="16"/>
+      <c r="ED3" s="21"/>
+      <c r="EE3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="EF3" s="7"/>
-      <c r="EG3" s="7" t="s">
+      <c r="EF3" s="15"/>
+      <c r="EG3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="EH3" s="8"/>
-      <c r="EI3" s="6" t="s">
+      <c r="EH3" s="16"/>
+      <c r="EI3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="EJ3" s="7"/>
-      <c r="EK3" s="7"/>
-      <c r="EL3" s="7" t="s">
+      <c r="EJ3" s="15"/>
+      <c r="EK3" s="15"/>
+      <c r="EL3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="EM3" s="7"/>
-      <c r="EN3" s="8"/>
-      <c r="EO3" s="6" t="s">
+      <c r="EM3" s="15"/>
+      <c r="EN3" s="16"/>
+      <c r="EO3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="EP3" s="7"/>
-      <c r="EQ3" s="7"/>
-      <c r="ER3" s="7" t="s">
+      <c r="EP3" s="15"/>
+      <c r="EQ3" s="15"/>
+      <c r="ER3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="ES3" s="7"/>
-      <c r="ET3" s="8"/>
-      <c r="EU3" s="22"/>
-      <c r="EV3" s="6" t="s">
+      <c r="ES3" s="15"/>
+      <c r="ET3" s="16"/>
+      <c r="EU3" s="21"/>
+      <c r="EV3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="EW3" s="8" t="s">
+      <c r="EW3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="EX3" s="22"/>
-      <c r="EY3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="EZ3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FA3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FB3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FC3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FD3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FE3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FF3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FG3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FH3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FI3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FJ3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FK3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FL3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FM3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FN3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FO3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FP3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="FQ3" s="6" t="s">
+      <c r="EX3" s="21"/>
+      <c r="EY3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="EZ3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FA3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FB3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FC3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FD3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FE3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FF3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FG3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FH3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FI3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FJ3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FK3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FL3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FM3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FN3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FO3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FP3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="FQ3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="FR3" s="8" t="s">
+      <c r="FR3" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="FS3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="FT3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="FU3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="FV3" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="V4" s="9" t="s">
+      <c r="FS3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="FT3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="FU3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="FV3" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="X4" s="10" t="s">
+      <c r="X4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Y4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Z4" s="10" t="s">
+      <c r="Z4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" s="10" t="s">
+      <c r="AA4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="10" t="s">
+      <c r="AB4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AC4" s="10" t="s">
+      <c r="AC4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AD4" s="10" t="s">
+      <c r="AD4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AE4" s="10" t="s">
+      <c r="AE4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AF4" s="10" t="s">
+      <c r="AF4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AG4" s="10" t="s">
+      <c r="AG4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AH4" s="10" t="s">
+      <c r="AH4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AI4" s="10" t="s">
+      <c r="AI4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AJ4" s="10" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AK4" s="11" t="s">
+      <c r="AK4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AL4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AS4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="AT4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AU4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AV4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AX4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AY4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="BB4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="BC4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BD4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BE4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BF4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BG4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BI4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="BK4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BL4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BM4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BN4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BO4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="BQ4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="BR4" s="6"/>
-      <c r="BS4" s="8"/>
-      <c r="BT4" s="6"/>
-      <c r="BU4" s="7"/>
-      <c r="BV4" s="8"/>
-      <c r="BW4" s="6"/>
-      <c r="BX4" s="8"/>
-      <c r="BY4" s="22"/>
-      <c r="BZ4" s="6"/>
-      <c r="CA4" s="8"/>
-      <c r="CB4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="CC4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CD4" s="10" t="s">
+      <c r="AL4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BQ4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR4" s="14"/>
+      <c r="BS4" s="16"/>
+      <c r="BT4" s="14"/>
+      <c r="BU4" s="15"/>
+      <c r="BV4" s="16"/>
+      <c r="BW4" s="14"/>
+      <c r="BX4" s="16"/>
+      <c r="BY4" s="21"/>
+      <c r="BZ4" s="14"/>
+      <c r="CA4" s="16"/>
+      <c r="CB4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CC4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CD4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="CE4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="CF4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CG4" s="11" t="s">
+      <c r="CE4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CF4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CG4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="CH4" s="6"/>
-      <c r="CI4" s="8"/>
-      <c r="CJ4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="CK4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CL4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="CM4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CN4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="CO4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CP4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="CQ4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="CR4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="CS4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CT4" s="10" t="s">
+      <c r="CH4" s="14"/>
+      <c r="CI4" s="16"/>
+      <c r="CJ4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CK4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CO4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CP4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CQ4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="CR4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="CS4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CT4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="CU4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="CV4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="CW4" s="11" t="s">
+      <c r="CU4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CV4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="CW4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="CX4" s="6"/>
-      <c r="CY4" s="8"/>
-      <c r="CZ4" s="6"/>
-      <c r="DA4" s="8"/>
-      <c r="DB4" s="22"/>
-      <c r="DC4" s="6"/>
-      <c r="DD4" s="8"/>
-      <c r="DE4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="DF4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="DG4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="DH4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="DI4" s="22"/>
-      <c r="DJ4" s="22"/>
-      <c r="DK4" s="6"/>
-      <c r="DL4" s="7"/>
-      <c r="DM4" s="7"/>
-      <c r="DN4" s="8"/>
-      <c r="DO4" s="22"/>
-      <c r="DP4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="DQ4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="DR4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="DS4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="DT4" s="22"/>
-      <c r="DU4" s="6"/>
-      <c r="DV4" s="8"/>
-      <c r="DW4" s="6"/>
-      <c r="DX4" s="8"/>
-      <c r="DY4" s="22"/>
-      <c r="DZ4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="EA4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="EB4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="EC4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="ED4" s="22"/>
-      <c r="EE4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="EF4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="EG4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="EH4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="EI4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="EJ4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="EK4" s="10" t="s">
+      <c r="CX4" s="14"/>
+      <c r="CY4" s="16"/>
+      <c r="CZ4" s="14"/>
+      <c r="DA4" s="16"/>
+      <c r="DB4" s="21"/>
+      <c r="DC4" s="14"/>
+      <c r="DD4" s="16"/>
+      <c r="DE4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="DF4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="DG4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="DH4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="DI4" s="21"/>
+      <c r="DJ4" s="21"/>
+      <c r="DK4" s="14"/>
+      <c r="DL4" s="15"/>
+      <c r="DM4" s="15"/>
+      <c r="DN4" s="16"/>
+      <c r="DO4" s="21"/>
+      <c r="DP4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="DQ4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="DR4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="DS4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="DT4" s="21"/>
+      <c r="DU4" s="14"/>
+      <c r="DV4" s="16"/>
+      <c r="DW4" s="14"/>
+      <c r="DX4" s="16"/>
+      <c r="DY4" s="21"/>
+      <c r="DZ4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="EA4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="EB4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="EC4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="ED4" s="21"/>
+      <c r="EE4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="EF4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="EG4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="EH4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="EI4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="EJ4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="EK4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="EL4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="EM4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="EN4" s="11" t="s">
+      <c r="EL4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="EM4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="EN4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="EO4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="EP4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="EQ4" s="10" t="s">
+      <c r="EO4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="EP4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="EQ4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="ER4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="ES4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="ET4" s="11" t="s">
+      <c r="ER4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="ES4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="ET4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="EU4" s="22"/>
-      <c r="EV4" s="6"/>
-      <c r="EW4" s="8"/>
-      <c r="EX4" s="22"/>
-      <c r="EY4" s="6"/>
-      <c r="EZ4" s="8"/>
-      <c r="FA4" s="6"/>
-      <c r="FB4" s="8"/>
-      <c r="FC4" s="6"/>
-      <c r="FD4" s="8"/>
-      <c r="FE4" s="6"/>
-      <c r="FF4" s="8"/>
-      <c r="FG4" s="6"/>
-      <c r="FH4" s="8"/>
-      <c r="FI4" s="6"/>
-      <c r="FJ4" s="8"/>
-      <c r="FK4" s="6"/>
-      <c r="FL4" s="8"/>
-      <c r="FM4" s="6"/>
-      <c r="FN4" s="8"/>
-      <c r="FO4" s="6"/>
-      <c r="FP4" s="8"/>
-      <c r="FQ4" s="6"/>
-      <c r="FR4" s="8"/>
-      <c r="FS4" s="6"/>
-      <c r="FT4" s="7"/>
-      <c r="FU4" s="7"/>
-      <c r="FV4" s="8"/>
-    </row>
-    <row r="5" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="12" t="s">
+      <c r="EU4" s="21"/>
+      <c r="EV4" s="14"/>
+      <c r="EW4" s="16"/>
+      <c r="EX4" s="21"/>
+      <c r="EY4" s="14"/>
+      <c r="EZ4" s="16"/>
+      <c r="FA4" s="14"/>
+      <c r="FB4" s="16"/>
+      <c r="FC4" s="14"/>
+      <c r="FD4" s="16"/>
+      <c r="FE4" s="14"/>
+      <c r="FF4" s="16"/>
+      <c r="FG4" s="14"/>
+      <c r="FH4" s="16"/>
+      <c r="FI4" s="14"/>
+      <c r="FJ4" s="16"/>
+      <c r="FK4" s="14"/>
+      <c r="FL4" s="16"/>
+      <c r="FM4" s="14"/>
+      <c r="FN4" s="16"/>
+      <c r="FO4" s="14"/>
+      <c r="FP4" s="16"/>
+      <c r="FQ4" s="14"/>
+      <c r="FR4" s="16"/>
+      <c r="FS4" s="14"/>
+      <c r="FT4" s="15"/>
+      <c r="FU4" s="15"/>
+      <c r="FV4" s="16"/>
+    </row>
+    <row r="5" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="14" t="s">
+      <c r="U5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="X5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="Z5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AA5" s="13" t="s">
+      <c r="AA5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AB5" s="13" t="s">
+      <c r="AB5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AC5" s="13" t="s">
+      <c r="AC5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AD5" s="13" t="s">
+      <c r="AD5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AE5" s="13" t="s">
+      <c r="AE5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AF5" s="13" t="s">
+      <c r="AF5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AG5" s="13" t="s">
+      <c r="AG5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AH5" s="13" t="s">
+      <c r="AH5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AI5" s="13" t="s">
+      <c r="AI5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AJ5" s="13" t="s">
+      <c r="AJ5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AK5" s="14" t="s">
+      <c r="AK5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AL5" s="12" t="s">
+      <c r="AL5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AM5" s="13" t="s">
+      <c r="AM5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AN5" s="13" t="s">
+      <c r="AN5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AO5" s="13" t="s">
+      <c r="AO5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="AP5" s="13" t="s">
+      <c r="AP5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AQ5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AR5" s="13" t="s">
+      <c r="AR5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AS5" s="14" t="s">
+      <c r="AS5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AT5" s="12" t="s">
+      <c r="AT5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AU5" s="13" t="s">
+      <c r="AU5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AV5" s="13" t="s">
+      <c r="AV5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AW5" s="13" t="s">
+      <c r="AW5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AX5" s="13" t="s">
+      <c r="AX5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AY5" s="13" t="s">
+      <c r="AY5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AZ5" s="13" t="s">
+      <c r="AZ5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BA5" s="14" t="s">
+      <c r="BA5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BB5" s="12" t="s">
+      <c r="BB5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="BC5" s="13" t="s">
+      <c r="BC5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BD5" s="13" t="s">
+      <c r="BD5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BE5" s="13" t="s">
+      <c r="BE5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BF5" s="13" t="s">
+      <c r="BF5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BG5" s="13" t="s">
+      <c r="BG5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BH5" s="13" t="s">
+      <c r="BH5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BI5" s="14" t="s">
+      <c r="BI5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BJ5" s="12" t="s">
+      <c r="BJ5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="BK5" s="13" t="s">
+      <c r="BK5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BL5" s="13" t="s">
+      <c r="BL5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="BM5" s="13" t="s">
+      <c r="BM5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="BN5" s="13" t="s">
+      <c r="BN5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="BO5" s="13" t="s">
+      <c r="BO5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="BP5" s="13" t="s">
+      <c r="BP5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="BQ5" s="14" t="s">
+      <c r="BQ5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="BR5" s="12" t="s">
+      <c r="BR5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="BS5" s="14" t="s">
+      <c r="BS5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="BT5" s="12" t="s">
+      <c r="BT5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="BU5" s="13" t="s">
+      <c r="BU5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="BV5" s="14" t="s">
+      <c r="BV5" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="BW5" s="12" t="s">
+      <c r="BW5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="BX5" s="14" t="s">
+      <c r="BX5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="BY5" s="23" t="s">
+      <c r="BY5" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="BZ5" s="12" t="s">
+      <c r="BZ5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="CA5" s="14" t="s">
+      <c r="CA5" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="CB5" s="12" t="s">
+      <c r="CB5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="CC5" s="13" t="s">
+      <c r="CC5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="CD5" s="13" t="s">
+      <c r="CD5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="CE5" s="13" t="s">
+      <c r="CE5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="CF5" s="13" t="s">
+      <c r="CF5" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="CG5" s="14" t="s">
+      <c r="CG5" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="CH5" s="12" t="s">
+      <c r="CH5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="CI5" s="14" t="s">
+      <c r="CI5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="CJ5" s="12" t="s">
+      <c r="CJ5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="CK5" s="13" t="s">
+      <c r="CK5" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="CL5" s="13" t="s">
+      <c r="CL5" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="CM5" s="13" t="s">
+      <c r="CM5" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="CN5" s="13" t="s">
+      <c r="CN5" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="CO5" s="13" t="s">
+      <c r="CO5" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="CP5" s="13" t="s">
+      <c r="CP5" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="CQ5" s="14" t="s">
+      <c r="CQ5" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="CR5" s="12" t="s">
+      <c r="CR5" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="CS5" s="13" t="s">
+      <c r="CS5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="CT5" s="13" t="s">
+      <c r="CT5" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="CU5" s="13" t="s">
+      <c r="CU5" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="CV5" s="13" t="s">
+      <c r="CV5" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="CW5" s="14" t="s">
+      <c r="CW5" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="CX5" s="12" t="s">
+      <c r="CX5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="CY5" s="14" t="s">
+      <c r="CY5" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="CZ5" s="12" t="s">
+      <c r="CZ5" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="DA5" s="14" t="s">
+      <c r="DA5" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="DB5" s="23" t="s">
+      <c r="DB5" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="DC5" s="12" t="s">
+      <c r="DC5" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="DD5" s="14" t="s">
+      <c r="DD5" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="DE5" s="12" t="s">
+      <c r="DE5" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="DF5" s="13" t="s">
+      <c r="DF5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="DG5" s="13" t="s">
+      <c r="DG5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="DH5" s="19" t="s">
+      <c r="DH5" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="DI5" s="23" t="s">
+      <c r="DI5" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="DJ5" s="23" t="s">
+      <c r="DJ5" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="DK5" s="12" t="s">
+      <c r="DK5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="DL5" s="13" t="s">
+      <c r="DL5" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="DM5" s="13" t="s">
+      <c r="DM5" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="DN5" s="14" t="s">
+      <c r="DN5" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="DO5" s="23" t="s">
+      <c r="DO5" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="DP5" s="12" t="s">
+      <c r="DP5" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="DQ5" s="13" t="s">
+      <c r="DQ5" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="DR5" s="13" t="s">
+      <c r="DR5" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="DS5" s="14" t="s">
+      <c r="DS5" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="DT5" s="23" t="s">
+      <c r="DT5" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="DU5" s="12" t="s">
+      <c r="DU5" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="DV5" s="14" t="s">
+      <c r="DV5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="DW5" s="12" t="s">
+      <c r="DW5" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="DX5" s="14" t="s">
+      <c r="DX5" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="DY5" s="23" t="s">
+      <c r="DY5" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="DZ5" s="12" t="s">
+      <c r="DZ5" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="EA5" s="13" t="s">
+      <c r="EA5" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="EB5" s="13" t="s">
+      <c r="EB5" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="EC5" s="14" t="s">
+      <c r="EC5" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="ED5" s="23" t="s">
+      <c r="ED5" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="EE5" s="12" t="s">
+      <c r="EE5" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="EF5" s="13" t="s">
+      <c r="EF5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="EG5" s="13" t="s">
+      <c r="EG5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="EH5" s="14" t="s">
+      <c r="EH5" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="EI5" s="12" t="s">
+      <c r="EI5" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="EJ5" s="13" t="s">
+      <c r="EJ5" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="EK5" s="13" t="s">
+      <c r="EK5" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="EL5" s="13" t="s">
+      <c r="EL5" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="EM5" s="13" t="s">
+      <c r="EM5" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="EN5" s="14" t="s">
+      <c r="EN5" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="EO5" s="12" t="s">
+      <c r="EO5" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="EP5" s="13" t="s">
+      <c r="EP5" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="EQ5" s="13" t="s">
+      <c r="EQ5" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="ER5" s="13" t="s">
+      <c r="ER5" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="ES5" s="13" t="s">
+      <c r="ES5" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="ET5" s="14" t="s">
+      <c r="ET5" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="EU5" s="23" t="s">
+      <c r="EU5" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="EV5" s="12" t="s">
+      <c r="EV5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="EW5" s="14" t="s">
+      <c r="EW5" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="EX5" s="23" t="s">
+      <c r="EX5" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="EY5" s="12" t="s">
+      <c r="EY5" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="EZ5" s="14" t="s">
+      <c r="EZ5" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="FA5" s="12" t="s">
+      <c r="FA5" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="FB5" s="14" t="s">
+      <c r="FB5" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="FC5" s="12" t="s">
+      <c r="FC5" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="FD5" s="14" t="s">
+      <c r="FD5" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="FE5" s="12" t="s">
+      <c r="FE5" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="FF5" s="14" t="s">
+      <c r="FF5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="FG5" s="12" t="s">
+      <c r="FG5" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="FH5" s="14" t="s">
+      <c r="FH5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="FI5" s="12" t="s">
+      <c r="FI5" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="FJ5" s="14" t="s">
+      <c r="FJ5" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="FK5" s="12" t="s">
+      <c r="FK5" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="FL5" s="14" t="s">
+      <c r="FL5" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="FM5" s="12" t="s">
+      <c r="FM5" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="FN5" s="14" t="s">
+      <c r="FN5" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="FO5" s="12" t="s">
+      <c r="FO5" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="FP5" s="14" t="s">
+      <c r="FP5" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="FQ5" s="12" t="s">
+      <c r="FQ5" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="FR5" s="14" t="s">
+      <c r="FR5" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="FS5" s="12" t="s">
+      <c r="FS5" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="FT5" s="13" t="s">
+      <c r="FT5" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="FU5" s="13" t="s">
+      <c r="FU5" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="FV5" s="14" t="s">
+      <c r="FV5" s="7" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="11" t="s">
+    <row r="7" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="21"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
+    <row r="8" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="21"/>
+      <c r="C8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="14" t="s">
+    <row r="9" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="25"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="CM9" s="1"/>
-      <c r="CN9" s="1"/>
-    </row>
-    <row r="10" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="CM9" s="22"/>
+      <c r="CN9" s="22"/>
+    </row>
+    <row r="10" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="11" t="s">
+    <row r="11" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7" t="s">
+    <row r="12" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="11" t="s">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="11" t="s">
+    <row r="13" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="7" t="s">
+    <row r="14" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="11" t="s">
+    <row r="15" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="7" t="s">
+    <row r="16" spans="2:178" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="D16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="11" t="s">
+    <row r="17" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="7" t="s">
+    <row r="18" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="14"/>
+      <c r="C18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="11" t="s">
+    <row r="19" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7" t="s">
+    <row r="20" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="14"/>
+      <c r="C20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="14" t="s">
+    <row r="21" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="24"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="22" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="14"/>
+      <c r="C26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="14"/>
+      <c r="C30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="14"/>
+      <c r="C34" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="24"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="14"/>
+      <c r="C40" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="14"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="14"/>
+      <c r="C42" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="14"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="14"/>
+      <c r="C44" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="24"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="14"/>
+      <c r="C48" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="14"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="14"/>
+      <c r="C50" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="14"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="14"/>
+      <c r="C52" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="24"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="14"/>
+      <c r="C56" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="14"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="14"/>
+      <c r="C58" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="14"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="14"/>
+      <c r="C60" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="24"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="14"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="14"/>
+      <c r="C64" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="14"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="14"/>
+      <c r="C66" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="14"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="14"/>
+      <c r="C68" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="24"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="18"/>
+      <c r="E70" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="24"/>
+      <c r="C71" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" s="23"/>
+      <c r="E71" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="18"/>
+      <c r="E72" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="14"/>
+      <c r="C73" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="15"/>
+      <c r="E73" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="24"/>
+      <c r="C74" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="23"/>
+      <c r="E74" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="18"/>
+      <c r="E75" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="24"/>
+      <c r="C76" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="23"/>
+      <c r="E76" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="24"/>
+      <c r="C79" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="23"/>
+      <c r="E79" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="14"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="14"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="14"/>
+      <c r="C83" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="14"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="24"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="18"/>
+      <c r="E86" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="24"/>
+      <c r="C87" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" s="23"/>
+      <c r="E87" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="14"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="14"/>
+      <c r="C90" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="14"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="14"/>
+      <c r="C92" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="14"/>
+      <c r="C94" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="24"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="14"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="14"/>
+      <c r="C99" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="14"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="24"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="18"/>
+      <c r="E102" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="24"/>
+      <c r="C103" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="23"/>
+      <c r="E103" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="18"/>
+      <c r="E104" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="24"/>
+      <c r="C105" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" s="23"/>
+      <c r="E105" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106" s="27"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="28" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="18"/>
+      <c r="E107" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="24"/>
+      <c r="C108" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="23"/>
+      <c r="E108" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="14"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="14"/>
+      <c r="C111" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="24"/>
+      <c r="C112" s="23"/>
+      <c r="D112" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="C113" s="27"/>
+      <c r="D113" s="27"/>
+      <c r="E113" s="28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C114" s="27"/>
+      <c r="D114" s="27"/>
+      <c r="E114" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="14"/>
+      <c r="C116" s="15"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="14"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="24"/>
+      <c r="C118" s="23"/>
+      <c r="D118" s="23"/>
+      <c r="E118" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C119" s="27"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C120" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="14"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="14"/>
+      <c r="C122" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="24"/>
+      <c r="C123" s="23"/>
+      <c r="D123" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" s="27"/>
+      <c r="D124" s="27"/>
+      <c r="E124" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125" s="18"/>
+      <c r="E125" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="24"/>
+      <c r="C126" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126" s="23"/>
+      <c r="E126" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D127" s="18"/>
+      <c r="E127" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="24"/>
+      <c r="C128" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128" s="23"/>
+      <c r="E128" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="C129" s="27"/>
+      <c r="D129" s="27"/>
+      <c r="E129" s="28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="14"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B132" s="14"/>
+      <c r="C132" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="24"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B134" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C134" s="27"/>
+      <c r="D134" s="27"/>
+      <c r="E134" s="28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B135" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="14"/>
+      <c r="C136" s="15"/>
+      <c r="D136" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="14"/>
+      <c r="C137" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="24"/>
+      <c r="C138" s="23"/>
+      <c r="D138" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C139" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="14"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="14"/>
+      <c r="C141" s="15"/>
+      <c r="D141" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="14"/>
+      <c r="C142" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="14"/>
+      <c r="C143" s="15"/>
+      <c r="D143" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="24"/>
+      <c r="C144" s="23"/>
+      <c r="D144" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C145" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="14"/>
+      <c r="C146" s="15"/>
+      <c r="D146" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="14"/>
+      <c r="C147" s="15"/>
+      <c r="D147" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="14"/>
+      <c r="C148" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="14"/>
+      <c r="C149" s="15"/>
+      <c r="D149" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="24"/>
+      <c r="C150" s="23"/>
+      <c r="D150" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="C151" s="27"/>
+      <c r="D151" s="27"/>
+      <c r="E151" s="28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C152" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D152" s="18"/>
+      <c r="E152" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="24"/>
+      <c r="C153" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" s="23"/>
+      <c r="E153" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C154" s="27"/>
+      <c r="D154" s="27"/>
+      <c r="E154" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C155" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="18"/>
+      <c r="E155" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="24"/>
+      <c r="C156" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" s="23"/>
+      <c r="E156" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C157" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="18"/>
+      <c r="E157" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="24"/>
+      <c r="C158" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" s="23"/>
+      <c r="E158" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C159" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="18"/>
+      <c r="E159" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="24"/>
+      <c r="C160" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D160" s="23"/>
+      <c r="E160" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C161" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="18"/>
+      <c r="E161" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="24"/>
+      <c r="C162" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D162" s="23"/>
+      <c r="E162" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C163" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="18"/>
+      <c r="E163" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="24"/>
+      <c r="C164" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D164" s="23"/>
+      <c r="E164" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C165" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="18"/>
+      <c r="E165" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="24"/>
+      <c r="C166" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="23"/>
+      <c r="E166" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C167" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="18"/>
+      <c r="E167" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="24"/>
+      <c r="C168" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D168" s="23"/>
+      <c r="E168" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C169" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="18"/>
+      <c r="E169" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="24"/>
+      <c r="C170" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D170" s="23"/>
+      <c r="E170" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C171" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="18"/>
+      <c r="E171" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="24"/>
+      <c r="C172" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D172" s="23"/>
+      <c r="E172" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C173" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D173" s="18"/>
+      <c r="E173" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="24"/>
+      <c r="C174" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D174" s="23"/>
+      <c r="E174" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C175" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="18"/>
+      <c r="E175" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B176" s="14"/>
+      <c r="C176" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D176" s="15"/>
+      <c r="E176" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B177" s="14"/>
+      <c r="C177" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="15"/>
+      <c r="E177" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="24"/>
+      <c r="C178" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D178" s="23"/>
+      <c r="E178" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="156">
-    <mergeCell ref="FS3:FS4"/>
-    <mergeCell ref="FT3:FT4"/>
-    <mergeCell ref="FU3:FU4"/>
-    <mergeCell ref="FV3:FV4"/>
-    <mergeCell ref="FS2:FV2"/>
-    <mergeCell ref="FO2:FP2"/>
-    <mergeCell ref="FO3:FO4"/>
-    <mergeCell ref="FP3:FP4"/>
-    <mergeCell ref="FQ2:FR2"/>
-    <mergeCell ref="FQ3:FQ4"/>
-    <mergeCell ref="FR3:FR4"/>
-    <mergeCell ref="FK2:FL2"/>
-    <mergeCell ref="FK3:FK4"/>
-    <mergeCell ref="FL3:FL4"/>
-    <mergeCell ref="FM2:FN2"/>
-    <mergeCell ref="FM3:FM4"/>
-    <mergeCell ref="FN3:FN4"/>
-    <mergeCell ref="FG2:FH2"/>
-    <mergeCell ref="FG3:FG4"/>
-    <mergeCell ref="FH3:FH4"/>
-    <mergeCell ref="FI2:FJ2"/>
-    <mergeCell ref="FI3:FI4"/>
-    <mergeCell ref="FJ3:FJ4"/>
-    <mergeCell ref="FC2:FD2"/>
-    <mergeCell ref="FC3:FC4"/>
-    <mergeCell ref="FD3:FD4"/>
-    <mergeCell ref="FE2:FF2"/>
-    <mergeCell ref="FE3:FE4"/>
-    <mergeCell ref="FF3:FF4"/>
-    <mergeCell ref="EX2:EX4"/>
-    <mergeCell ref="EY2:EZ2"/>
-    <mergeCell ref="EY3:EY4"/>
-    <mergeCell ref="EZ3:EZ4"/>
-    <mergeCell ref="FA2:FB2"/>
-    <mergeCell ref="FA3:FA4"/>
-    <mergeCell ref="FB3:FB4"/>
-    <mergeCell ref="EO2:ET2"/>
-    <mergeCell ref="EO3:EQ3"/>
-    <mergeCell ref="ER3:ET3"/>
-    <mergeCell ref="EU2:EU4"/>
-    <mergeCell ref="EV3:EV4"/>
-    <mergeCell ref="EW3:EW4"/>
-    <mergeCell ref="EV2:EW2"/>
-    <mergeCell ref="ED2:ED4"/>
-    <mergeCell ref="EE2:EH2"/>
-    <mergeCell ref="EE3:EF3"/>
-    <mergeCell ref="EG3:EH3"/>
-    <mergeCell ref="EI2:EN2"/>
-    <mergeCell ref="EI3:EK3"/>
-    <mergeCell ref="EL3:EN3"/>
-    <mergeCell ref="DW2:DX2"/>
-    <mergeCell ref="DW3:DW4"/>
-    <mergeCell ref="DX3:DX4"/>
-    <mergeCell ref="DY2:DY4"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="DZ2:EC2"/>
-    <mergeCell ref="DO2:DO4"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="DP2:DS2"/>
-    <mergeCell ref="DT2:DT4"/>
-    <mergeCell ref="DU2:DV2"/>
-    <mergeCell ref="DU3:DU4"/>
-    <mergeCell ref="DV3:DV4"/>
-    <mergeCell ref="DE3:DF3"/>
-    <mergeCell ref="DG3:DH3"/>
-    <mergeCell ref="DE2:DH2"/>
-    <mergeCell ref="DI2:DI4"/>
-    <mergeCell ref="DJ2:DJ4"/>
-    <mergeCell ref="DK2:DN4"/>
-    <mergeCell ref="CZ3:CZ4"/>
-    <mergeCell ref="DA3:DA4"/>
-    <mergeCell ref="CZ2:DA2"/>
-    <mergeCell ref="DB2:DB4"/>
-    <mergeCell ref="DC2:DD2"/>
-    <mergeCell ref="DC3:DC4"/>
-    <mergeCell ref="DD3:DD4"/>
-    <mergeCell ref="CR3:CT3"/>
-    <mergeCell ref="CU3:CW3"/>
-    <mergeCell ref="CR2:CW2"/>
-    <mergeCell ref="CX3:CX4"/>
-    <mergeCell ref="CY3:CY4"/>
-    <mergeCell ref="CX2:CY2"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="CJ2:CQ2"/>
-    <mergeCell ref="CM9:CN9"/>
-    <mergeCell ref="CB3:CD3"/>
-    <mergeCell ref="CE3:CG3"/>
-    <mergeCell ref="CB2:CG2"/>
-    <mergeCell ref="CH3:CH4"/>
-    <mergeCell ref="CI3:CI4"/>
-    <mergeCell ref="CH2:CI2"/>
-    <mergeCell ref="BW3:BW4"/>
-    <mergeCell ref="BX3:BX4"/>
-    <mergeCell ref="BW2:BX2"/>
-    <mergeCell ref="BY2:BY4"/>
-    <mergeCell ref="BZ3:BZ4"/>
-    <mergeCell ref="CA3:CA4"/>
-    <mergeCell ref="BZ2:CA2"/>
+  <mergeCells count="290">
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="B173:B174"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="B175:B178"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="B154:D154"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="B135:B138"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="C139:C141"/>
+    <mergeCell ref="C142:C144"/>
+    <mergeCell ref="B145:B150"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="C148:C150"/>
+    <mergeCell ref="B124:D124"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="B109:B112"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="B115:D118"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="B88:B95"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B96:B101"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="C99:C101"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="B62:B69"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B54:B61"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B22:B37"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="B38:B45"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B10:B21"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B2:E5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="V2:AK2"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="AL2:AS2"/>
+    <mergeCell ref="AT2:BA2"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="AZ3:BA3"/>
     <mergeCell ref="BR2:BS2"/>
     <mergeCell ref="BR3:BR4"/>
     <mergeCell ref="BS3:BS4"/>
@@ -3133,43 +4968,111 @@
     <mergeCell ref="BL3:BM3"/>
     <mergeCell ref="BN3:BO3"/>
     <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="AL2:AS2"/>
-    <mergeCell ref="AT2:BA2"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="V2:AK2"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AD3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="B10:B21"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B2:E5"/>
-    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="CM9:CN9"/>
+    <mergeCell ref="CB3:CD3"/>
+    <mergeCell ref="CE3:CG3"/>
+    <mergeCell ref="CB2:CG2"/>
+    <mergeCell ref="CH3:CH4"/>
+    <mergeCell ref="CI3:CI4"/>
+    <mergeCell ref="CH2:CI2"/>
+    <mergeCell ref="BW3:BW4"/>
+    <mergeCell ref="BX3:BX4"/>
+    <mergeCell ref="BW2:BX2"/>
+    <mergeCell ref="BY2:BY4"/>
+    <mergeCell ref="BZ3:BZ4"/>
+    <mergeCell ref="CA3:CA4"/>
+    <mergeCell ref="BZ2:CA2"/>
+    <mergeCell ref="CR3:CT3"/>
+    <mergeCell ref="CU3:CW3"/>
+    <mergeCell ref="CR2:CW2"/>
+    <mergeCell ref="CX3:CX4"/>
+    <mergeCell ref="CY3:CY4"/>
+    <mergeCell ref="CX2:CY2"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="CJ2:CQ2"/>
+    <mergeCell ref="DE3:DF3"/>
+    <mergeCell ref="DG3:DH3"/>
+    <mergeCell ref="DE2:DH2"/>
+    <mergeCell ref="DI2:DI4"/>
+    <mergeCell ref="DJ2:DJ4"/>
+    <mergeCell ref="DK2:DN4"/>
+    <mergeCell ref="CZ3:CZ4"/>
+    <mergeCell ref="DA3:DA4"/>
+    <mergeCell ref="CZ2:DA2"/>
+    <mergeCell ref="DB2:DB4"/>
+    <mergeCell ref="DC2:DD2"/>
+    <mergeCell ref="DC3:DC4"/>
+    <mergeCell ref="DD3:DD4"/>
+    <mergeCell ref="DW2:DX2"/>
+    <mergeCell ref="DW3:DW4"/>
+    <mergeCell ref="DX3:DX4"/>
+    <mergeCell ref="DY2:DY4"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="DZ2:EC2"/>
+    <mergeCell ref="DO2:DO4"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="DP2:DS2"/>
+    <mergeCell ref="DT2:DT4"/>
+    <mergeCell ref="DU2:DV2"/>
+    <mergeCell ref="DU3:DU4"/>
+    <mergeCell ref="DV3:DV4"/>
+    <mergeCell ref="EO2:ET2"/>
+    <mergeCell ref="EO3:EQ3"/>
+    <mergeCell ref="ER3:ET3"/>
+    <mergeCell ref="EU2:EU4"/>
+    <mergeCell ref="EV3:EV4"/>
+    <mergeCell ref="EW3:EW4"/>
+    <mergeCell ref="EV2:EW2"/>
+    <mergeCell ref="ED2:ED4"/>
+    <mergeCell ref="EE2:EH2"/>
+    <mergeCell ref="EE3:EF3"/>
+    <mergeCell ref="EG3:EH3"/>
+    <mergeCell ref="EI2:EN2"/>
+    <mergeCell ref="EI3:EK3"/>
+    <mergeCell ref="EL3:EN3"/>
+    <mergeCell ref="FC2:FD2"/>
+    <mergeCell ref="FC3:FC4"/>
+    <mergeCell ref="FD3:FD4"/>
+    <mergeCell ref="FE2:FF2"/>
+    <mergeCell ref="FE3:FE4"/>
+    <mergeCell ref="FF3:FF4"/>
+    <mergeCell ref="EX2:EX4"/>
+    <mergeCell ref="EY2:EZ2"/>
+    <mergeCell ref="EY3:EY4"/>
+    <mergeCell ref="EZ3:EZ4"/>
+    <mergeCell ref="FA2:FB2"/>
+    <mergeCell ref="FA3:FA4"/>
+    <mergeCell ref="FB3:FB4"/>
+    <mergeCell ref="FK2:FL2"/>
+    <mergeCell ref="FK3:FK4"/>
+    <mergeCell ref="FL3:FL4"/>
+    <mergeCell ref="FM2:FN2"/>
+    <mergeCell ref="FM3:FM4"/>
+    <mergeCell ref="FN3:FN4"/>
+    <mergeCell ref="FG2:FH2"/>
+    <mergeCell ref="FG3:FG4"/>
+    <mergeCell ref="FH3:FH4"/>
+    <mergeCell ref="FI2:FJ2"/>
+    <mergeCell ref="FI3:FI4"/>
+    <mergeCell ref="FJ3:FJ4"/>
+    <mergeCell ref="FS3:FS4"/>
+    <mergeCell ref="FT3:FT4"/>
+    <mergeCell ref="FU3:FU4"/>
+    <mergeCell ref="FV3:FV4"/>
+    <mergeCell ref="FS2:FV2"/>
+    <mergeCell ref="FO2:FP2"/>
+    <mergeCell ref="FO3:FO4"/>
+    <mergeCell ref="FP3:FP4"/>
+    <mergeCell ref="FQ2:FR2"/>
+    <mergeCell ref="FQ3:FQ4"/>
+    <mergeCell ref="FR3:FR4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>